--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129966457</v>
+        <v>129966450</v>
       </c>
       <c r="B12" t="n">
         <v>79084</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490338</v>
+        <v>490298</v>
       </c>
       <c r="R12" t="n">
-        <v>7015507</v>
+        <v>7015548</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2090,7 +2090,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129966450</v>
+        <v>129966451</v>
       </c>
       <c r="B13" t="n">
         <v>79084</v>
@@ -2131,7 +2131,7 @@
         <v>490298</v>
       </c>
       <c r="R13" t="n">
-        <v>7015548</v>
+        <v>7015578</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2221,7 +2221,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129966451</v>
+        <v>129966457</v>
       </c>
       <c r="B14" t="n">
         <v>79084</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490298</v>
+        <v>490338</v>
       </c>
       <c r="R14" t="n">
-        <v>7015578</v>
+        <v>7015507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2614,10 +2614,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129966444</v>
+        <v>129966459</v>
       </c>
       <c r="B17" t="n">
-        <v>91622</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2625,26 +2625,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490286</v>
+        <v>490355</v>
       </c>
       <c r="R17" t="n">
-        <v>7015529</v>
+        <v>7015525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2690,11 +2690,6 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2707,7 +2702,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2722,12 +2717,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2876,10 +2871,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129966459</v>
+        <v>129966444</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>91622</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2887,26 +2882,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2914,10 +2909,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490355</v>
+        <v>490286</v>
       </c>
       <c r="R19" t="n">
-        <v>7015525</v>
+        <v>7015529</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2952,6 +2947,11 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129966455</v>
+        <v>129966461</v>
       </c>
       <c r="B21" t="n">
         <v>79084</v>
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490297</v>
+        <v>490240</v>
       </c>
       <c r="R21" t="n">
-        <v>7015530</v>
+        <v>7015520</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3240,7 +3240,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129966461</v>
+        <v>129966455</v>
       </c>
       <c r="B22" t="n">
         <v>79084</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490240</v>
+        <v>490297</v>
       </c>
       <c r="R22" t="n">
-        <v>7015520</v>
+        <v>7015530</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">

--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129966433</v>
+        <v>129966434</v>
       </c>
       <c r="B7" t="n">
         <v>57895</v>
@@ -1360,17 +1360,21 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höljebäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490256</v>
+        <v>490346</v>
       </c>
       <c r="R7" t="n">
-        <v>7015540</v>
+        <v>7015608</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1411,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i flerskiktad barrblandskog.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad granskog med björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,7 +1425,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1439,7 +1443,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129966434</v>
+        <v>129966433</v>
       </c>
       <c r="B8" t="n">
         <v>57895</v>
@@ -1479,21 +1483,17 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höljebäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490346</v>
+        <v>490256</v>
       </c>
       <c r="R8" t="n">
-        <v>7015608</v>
+        <v>7015540</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad granskog med björkhögstubbar.</t>
+          <t>2 individer med lockläte i flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129966456</v>
+        <v>129966457</v>
       </c>
       <c r="B11" t="n">
         <v>79084</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490326</v>
+        <v>490338</v>
       </c>
       <c r="R11" t="n">
-        <v>7015529</v>
+        <v>7015507</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2221,7 +2221,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129966457</v>
+        <v>129966456</v>
       </c>
       <c r="B14" t="n">
         <v>79084</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490338</v>
+        <v>490326</v>
       </c>
       <c r="R14" t="n">
-        <v>7015507</v>
+        <v>7015529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2614,10 +2614,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129966459</v>
+        <v>129966444</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>91622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2625,26 +2625,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490355</v>
+        <v>490286</v>
       </c>
       <c r="R17" t="n">
-        <v>7015525</v>
+        <v>7015529</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2690,6 +2690,11 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2702,7 +2707,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2717,12 +2722,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2871,10 +2876,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129966444</v>
+        <v>129966459</v>
       </c>
       <c r="B19" t="n">
-        <v>91622</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2882,26 +2887,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2909,10 +2914,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490286</v>
+        <v>490355</v>
       </c>
       <c r="R19" t="n">
-        <v>7015529</v>
+        <v>7015525</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2947,11 +2952,6 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129966461</v>
+        <v>129966455</v>
       </c>
       <c r="B21" t="n">
         <v>79084</v>
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490240</v>
+        <v>490297</v>
       </c>
       <c r="R21" t="n">
-        <v>7015520</v>
+        <v>7015530</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3240,7 +3240,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129966455</v>
+        <v>129966461</v>
       </c>
       <c r="B22" t="n">
         <v>79084</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490297</v>
+        <v>490240</v>
       </c>
       <c r="R22" t="n">
-        <v>7015530</v>
+        <v>7015520</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">

--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -2614,10 +2614,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129966444</v>
+        <v>129966459</v>
       </c>
       <c r="B17" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2625,26 +2625,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490286</v>
+        <v>490355</v>
       </c>
       <c r="R17" t="n">
-        <v>7015529</v>
+        <v>7015525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2690,11 +2690,6 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2707,7 +2702,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2722,12 +2717,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2745,10 +2740,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129966454</v>
+        <v>129966444</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>91659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2756,26 +2751,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2783,10 +2778,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490327</v>
+        <v>490286</v>
       </c>
       <c r="R18" t="n">
-        <v>7015629</v>
+        <v>7015529</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2823,7 +2818,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Flera fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2838,7 +2833,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2853,12 +2848,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2876,7 +2871,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129966459</v>
+        <v>129966454</v>
       </c>
       <c r="B19" t="n">
         <v>79095</v>
@@ -2914,10 +2909,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490355</v>
+        <v>490327</v>
       </c>
       <c r="R19" t="n">
-        <v>7015525</v>
+        <v>7015629</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2950,6 +2945,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129966443</v>
+        <v>129966465</v>
       </c>
       <c r="B5" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,26 +1069,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490306</v>
+        <v>490307</v>
       </c>
       <c r="R5" t="n">
-        <v>7015525</v>
+        <v>7015467</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och 23 cm i brösthöjdsdiameter.</t>
+          <t>På en klen gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129966465</v>
+        <v>129966443</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>91659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,26 +1200,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490307</v>
+        <v>490306</v>
       </c>
       <c r="R6" t="n">
-        <v>7015467</v>
+        <v>7015525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en klen gran.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och 23 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129966465</v>
+        <v>129966443</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,26 +1069,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490307</v>
+        <v>490306</v>
       </c>
       <c r="R5" t="n">
-        <v>7015467</v>
+        <v>7015525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en klen gran.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och 23 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129966443</v>
+        <v>129966465</v>
       </c>
       <c r="B6" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,26 +1200,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490306</v>
+        <v>490307</v>
       </c>
       <c r="R6" t="n">
-        <v>7015525</v>
+        <v>7015467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och 23 cm i brösthöjdsdiameter.</t>
+          <t>På en klen gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
         <v>129966442</v>
       </c>
       <c r="B10" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129966457</v>
+        <v>129966450</v>
       </c>
       <c r="B11" t="n">
         <v>79095</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490338</v>
+        <v>490298</v>
       </c>
       <c r="R11" t="n">
-        <v>7015507</v>
+        <v>7015548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129966450</v>
+        <v>129966451</v>
       </c>
       <c r="B12" t="n">
         <v>79095</v>
@@ -2000,7 +2000,7 @@
         <v>490298</v>
       </c>
       <c r="R12" t="n">
-        <v>7015548</v>
+        <v>7015578</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2090,7 +2090,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129966451</v>
+        <v>129966457</v>
       </c>
       <c r="B13" t="n">
         <v>79095</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490298</v>
+        <v>490338</v>
       </c>
       <c r="R13" t="n">
-        <v>7015578</v>
+        <v>7015507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2352,10 +2352,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129966445</v>
+        <v>129966462</v>
       </c>
       <c r="B15" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2363,26 +2363,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490246</v>
+        <v>490297</v>
       </c>
       <c r="R15" t="n">
-        <v>7015504</v>
+        <v>7015502</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129966462</v>
+        <v>129966445</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2494,26 +2494,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490297</v>
+        <v>490246</v>
       </c>
       <c r="R16" t="n">
-        <v>7015502</v>
+        <v>7015504</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129966459</v>
+        <v>129966454</v>
       </c>
       <c r="B17" t="n">
         <v>79095</v>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490355</v>
+        <v>490327</v>
       </c>
       <c r="R17" t="n">
-        <v>7015525</v>
+        <v>7015629</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2688,6 +2688,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2740,10 +2745,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129966444</v>
+        <v>129966459</v>
       </c>
       <c r="B18" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2751,26 +2756,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2778,10 +2783,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490286</v>
+        <v>490355</v>
       </c>
       <c r="R18" t="n">
-        <v>7015529</v>
+        <v>7015525</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2816,11 +2821,6 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129966454</v>
+        <v>129966444</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2882,26 +2882,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490327</v>
+        <v>490286</v>
       </c>
       <c r="R19" t="n">
-        <v>7015629</v>
+        <v>7015529</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Flera fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
         <v>129966436</v>
       </c>
       <c r="B20" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129966449</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129966460</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>129966458</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>129966443</v>
       </c>
       <c r="B5" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>129966465</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>129966433</v>
       </c>
       <c r="B7" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>129966434</v>
       </c>
       <c r="B8" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129966463</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>129966442</v>
       </c>
       <c r="B10" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129966450</v>
+        <v>129966457</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490298</v>
+        <v>490338</v>
       </c>
       <c r="R11" t="n">
-        <v>7015548</v>
+        <v>7015507</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129966451</v>
+        <v>129966450</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>490298</v>
       </c>
       <c r="R12" t="n">
-        <v>7015578</v>
+        <v>7015548</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2090,10 +2090,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129966457</v>
+        <v>129966451</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490338</v>
+        <v>490298</v>
       </c>
       <c r="R13" t="n">
-        <v>7015507</v>
+        <v>7015578</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2224,7 +2224,7 @@
         <v>129966456</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129966462</v>
+        <v>129966445</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>91748</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2363,26 +2363,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490297</v>
+        <v>490246</v>
       </c>
       <c r="R15" t="n">
-        <v>7015502</v>
+        <v>7015504</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129966445</v>
+        <v>129966462</v>
       </c>
       <c r="B16" t="n">
-        <v>91661</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2494,26 +2494,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490246</v>
+        <v>490297</v>
       </c>
       <c r="R16" t="n">
-        <v>7015504</v>
+        <v>7015502</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129966454</v>
+        <v>129966444</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>91748</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2625,26 +2625,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490327</v>
+        <v>490286</v>
       </c>
       <c r="R17" t="n">
-        <v>7015629</v>
+        <v>7015529</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Flera fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129966459</v>
+        <v>129966454</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490355</v>
+        <v>490327</v>
       </c>
       <c r="R18" t="n">
-        <v>7015525</v>
+        <v>7015629</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2819,6 +2819,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2871,10 +2876,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129966444</v>
+        <v>129966459</v>
       </c>
       <c r="B19" t="n">
-        <v>91661</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2882,26 +2887,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2909,10 +2914,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490286</v>
+        <v>490355</v>
       </c>
       <c r="R19" t="n">
-        <v>7015529</v>
+        <v>7015525</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2947,11 +2952,6 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
         <v>129966436</v>
       </c>
       <c r="B20" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>129966455</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129966461</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>129966453</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>129966435</v>
       </c>
       <c r="B24" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -2352,10 +2352,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129966445</v>
+        <v>129966462</v>
       </c>
       <c r="B15" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2363,26 +2363,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490246</v>
+        <v>490297</v>
       </c>
       <c r="R15" t="n">
-        <v>7015504</v>
+        <v>7015502</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129966462</v>
+        <v>129966445</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2494,26 +2494,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490297</v>
+        <v>490246</v>
       </c>
       <c r="R16" t="n">
-        <v>7015502</v>
+        <v>7015504</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -1828,7 +1828,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129966457</v>
+        <v>129966450</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490338</v>
+        <v>490298</v>
       </c>
       <c r="R11" t="n">
-        <v>7015507</v>
+        <v>7015548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129966450</v>
+        <v>129966451</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -2000,7 +2000,7 @@
         <v>490298</v>
       </c>
       <c r="R12" t="n">
-        <v>7015548</v>
+        <v>7015578</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2090,7 +2090,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129966451</v>
+        <v>129966457</v>
       </c>
       <c r="B13" t="n">
         <v>79180</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490298</v>
+        <v>490338</v>
       </c>
       <c r="R13" t="n">
-        <v>7015578</v>
+        <v>7015507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2352,10 +2352,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129966462</v>
+        <v>129966445</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2363,26 +2363,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490297</v>
+        <v>490246</v>
       </c>
       <c r="R15" t="n">
-        <v>7015502</v>
+        <v>7015504</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129966445</v>
+        <v>129966462</v>
       </c>
       <c r="B16" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2494,26 +2494,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490246</v>
+        <v>490297</v>
       </c>
       <c r="R16" t="n">
-        <v>7015504</v>
+        <v>7015502</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129966433</v>
+        <v>129966434</v>
       </c>
       <c r="B7" t="n">
         <v>57985</v>
@@ -1360,17 +1360,21 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höljebäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490256</v>
+        <v>490346</v>
       </c>
       <c r="R7" t="n">
-        <v>7015540</v>
+        <v>7015608</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1411,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i flerskiktad barrblandskog.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad granskog med björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,7 +1425,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1439,7 +1443,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129966434</v>
+        <v>129966433</v>
       </c>
       <c r="B8" t="n">
         <v>57985</v>
@@ -1479,21 +1483,17 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höljebäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490346</v>
+        <v>490256</v>
       </c>
       <c r="R8" t="n">
-        <v>7015608</v>
+        <v>7015540</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad granskog med björkhögstubbar.</t>
+          <t>2 individer med lockläte i flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129966450</v>
+        <v>129966451</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1869,7 +1869,7 @@
         <v>490298</v>
       </c>
       <c r="R11" t="n">
-        <v>7015548</v>
+        <v>7015578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129966451</v>
+        <v>129966450</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -2000,7 +2000,7 @@
         <v>490298</v>
       </c>
       <c r="R12" t="n">
-        <v>7015578</v>
+        <v>7015548</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2614,10 +2614,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129966444</v>
+        <v>129966459</v>
       </c>
       <c r="B17" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2625,26 +2625,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490286</v>
+        <v>490355</v>
       </c>
       <c r="R17" t="n">
-        <v>7015529</v>
+        <v>7015525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2690,11 +2690,6 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2707,7 +2702,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2722,12 +2717,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2745,10 +2740,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129966454</v>
+        <v>129966444</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2756,26 +2751,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2783,10 +2778,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490327</v>
+        <v>490286</v>
       </c>
       <c r="R18" t="n">
-        <v>7015629</v>
+        <v>7015529</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2823,7 +2818,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Flera fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2838,7 +2833,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2853,12 +2848,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2876,7 +2871,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129966459</v>
+        <v>129966454</v>
       </c>
       <c r="B19" t="n">
         <v>79180</v>
@@ -2914,10 +2909,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490355</v>
+        <v>490327</v>
       </c>
       <c r="R19" t="n">
-        <v>7015525</v>
+        <v>7015629</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2950,6 +2945,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3109,7 +3109,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129966455</v>
+        <v>129966461</v>
       </c>
       <c r="B21" t="n">
         <v>79180</v>
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490297</v>
+        <v>490240</v>
       </c>
       <c r="R21" t="n">
-        <v>7015530</v>
+        <v>7015520</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3240,7 +3240,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129966461</v>
+        <v>129966455</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490240</v>
+        <v>490297</v>
       </c>
       <c r="R22" t="n">
-        <v>7015520</v>
+        <v>7015530</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">

--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129966449</v>
+        <v>129966442</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490241</v>
+        <v>490218</v>
       </c>
       <c r="R2" t="n">
-        <v>7015482</v>
+        <v>7015588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +755,11 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar i stambasen av en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,14 +810,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129966460</v>
+        <v>129966449</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -839,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490271</v>
+        <v>490241</v>
       </c>
       <c r="R3" t="n">
-        <v>7015531</v>
+        <v>7015482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,11 +884,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,14 +936,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129966458</v>
+        <v>129966450</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -970,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490315</v>
+        <v>490298</v>
       </c>
       <c r="R4" t="n">
-        <v>7015455</v>
+        <v>7015548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,6 +1012,11 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1020,7 +1029,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1058,37 +1067,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129966443</v>
+        <v>129966451</v>
       </c>
       <c r="B5" t="n">
-        <v>91748</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1096,10 +1105,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490306</v>
+        <v>490298</v>
       </c>
       <c r="R5" t="n">
-        <v>7015525</v>
+        <v>7015578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,7 +1145,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och 23 cm i brösthöjdsdiameter.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1160,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1166,12 +1175,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,14 +1198,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129966465</v>
+        <v>129966453</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1227,10 +1236,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490307</v>
+        <v>490335</v>
       </c>
       <c r="R6" t="n">
-        <v>7015467</v>
+        <v>7015588</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,7 +1276,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en klen gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1291,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1320,61 +1329,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129966434</v>
+        <v>129966454</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höljebäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490346</v>
+        <v>490327</v>
       </c>
       <c r="R7" t="n">
-        <v>7015608</v>
+        <v>7015629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1407,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad granskog med björkhögstubbar.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,12 +1416,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1443,46 +1460,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129966433</v>
+        <v>129966455</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1490,10 +1498,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490256</v>
+        <v>490297</v>
       </c>
       <c r="R8" t="n">
-        <v>7015540</v>
+        <v>7015530</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1530,7 +1538,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i flerskiktad barrblandskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,12 +1547,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,14 +1591,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129966463</v>
+        <v>129966456</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1600,10 +1629,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490319</v>
+        <v>490326</v>
       </c>
       <c r="R9" t="n">
-        <v>7015497</v>
+        <v>7015529</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,7 +1684,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1693,41 +1722,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129966442</v>
+        <v>129966457</v>
       </c>
       <c r="B10" t="n">
-        <v>91724</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1735,10 +1760,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490218</v>
+        <v>490338</v>
       </c>
       <c r="R10" t="n">
-        <v>7015588</v>
+        <v>7015507</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1775,7 +1800,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1805,12 +1830,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1828,14 +1853,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129966456</v>
+        <v>129966458</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1866,10 +1891,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490326</v>
+        <v>490315</v>
       </c>
       <c r="R11" t="n">
-        <v>7015529</v>
+        <v>7015455</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,11 +1929,6 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1921,7 +1941,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1959,14 +1979,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129966451</v>
+        <v>129966459</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1997,10 +2017,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490298</v>
+        <v>490355</v>
       </c>
       <c r="R12" t="n">
-        <v>7015578</v>
+        <v>7015525</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2033,11 +2053,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2090,14 +2105,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129966450</v>
+        <v>129966460</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2128,10 +2143,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490298</v>
+        <v>490271</v>
       </c>
       <c r="R13" t="n">
-        <v>7015548</v>
+        <v>7015531</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2183,7 +2198,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2221,14 +2236,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129966457</v>
+        <v>129966461</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2259,10 +2274,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490338</v>
+        <v>490240</v>
       </c>
       <c r="R14" t="n">
-        <v>7015507</v>
+        <v>7015520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2299,7 +2314,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2352,37 +2367,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129966445</v>
+        <v>129966462</v>
       </c>
       <c r="B15" t="n">
-        <v>91748</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2390,10 +2405,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490246</v>
+        <v>490297</v>
       </c>
       <c r="R15" t="n">
-        <v>7015504</v>
+        <v>7015502</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2430,7 +2445,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,7 +2460,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2460,12 +2475,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2483,14 +2498,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129966462</v>
+        <v>129966463</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2521,10 +2536,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490297</v>
+        <v>490319</v>
       </c>
       <c r="R16" t="n">
-        <v>7015502</v>
+        <v>7015497</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2576,7 +2591,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2614,14 +2629,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129966459</v>
+        <v>129966465</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2652,10 +2667,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490355</v>
+        <v>490307</v>
       </c>
       <c r="R17" t="n">
-        <v>7015525</v>
+        <v>7015467</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2688,6 +2703,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På en klen gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2740,10 +2760,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129966444</v>
+        <v>129966433</v>
       </c>
       <c r="B18" t="n">
-        <v>91748</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2751,24 +2771,33 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2778,10 +2807,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490286</v>
+        <v>490256</v>
       </c>
       <c r="R18" t="n">
-        <v>7015529</v>
+        <v>7015540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2818,7 +2847,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
+          <t>2 individer med lockläte i flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2827,33 +2856,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2871,10 +2879,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129966454</v>
+        <v>129966434</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2882,37 +2890,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Höljebäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490327</v>
+        <v>490346</v>
       </c>
       <c r="R19" t="n">
-        <v>7015629</v>
+        <v>7015608</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2949,7 +2970,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad granskog med björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2958,33 +2979,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3002,49 +3002,61 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129966436</v>
+        <v>129966435</v>
       </c>
       <c r="B20" t="n">
-        <v>97791</v>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Höljebäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490305</v>
+        <v>490278</v>
       </c>
       <c r="R20" t="n">
-        <v>7015538</v>
+        <v>7015492</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3079,19 +3091,23 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 2 födosökande individer med lockläte varav synobservation av en av dom. Fyndplatsen finns i flerskiktad barrblandskog med björkhögstubbar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3109,37 +3125,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129966461</v>
+        <v>129966436</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>97983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3147,10 +3164,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490240</v>
+        <v>490305</v>
       </c>
       <c r="R21" t="n">
-        <v>7015520</v>
+        <v>7015538</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3185,11 +3202,6 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3202,27 +3214,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3237,391 +3229,6 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>129966455</v>
-      </c>
-      <c r="B22" t="n">
-        <v>79180</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Höljebäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>490297</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7015530</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>129966453</v>
-      </c>
-      <c r="B23" t="n">
-        <v>79180</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Höljebäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>490335</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7015588</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>129966435</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57985</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Höljebäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>490278</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7015492</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 2 födosökande individer med lockläte varav synobservation av en av dom. Fyndplatsen finns i flerskiktad barrblandskog med björkhögstubbar.</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56934-2025 artfynd.xlsx
+++ b/artfynd/A 56934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966442</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -933,6 +943,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966449</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1064,6 +1079,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966450</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1195,6 +1215,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966451</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1326,6 +1351,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966453</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1457,6 +1487,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966454</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1588,6 +1623,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966455</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1719,6 +1759,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966456</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1850,6 +1895,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966457</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1976,6 +2026,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966458</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2102,6 +2157,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966459</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2233,6 +2293,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966460</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2364,6 +2429,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966461</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2495,6 +2565,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966462</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2626,6 +2701,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966463</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2757,6 +2837,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966465</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2876,6 +2961,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966433</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2999,6 +3089,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966434</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3122,6 +3217,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966435</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3229,8 +3329,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966436</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>